--- a/Reste à charge.xlsx
+++ b/Reste à charge.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rehl\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB01193F-61EB-4F90-9D3E-AA5FEE19EA92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F89F4A40-72F4-491D-9CC7-31588F5F5BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="35280" yWindow="2370" windowWidth="21600" windowHeight="11295" xr2:uid="{35AFCA5C-8CF8-4836-A71A-CBADB6DDEB25}"/>
   </bookViews>
@@ -458,7 +458,7 @@
         <v>2024</v>
       </c>
       <c r="B2" s="2">
-        <v>274</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -474,7 +474,7 @@
         <v>2026</v>
       </c>
       <c r="B4" s="3">
-        <v>298.75829034355343</v>
+        <v>298.30965821602149</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -482,7 +482,7 @@
         <v>2027</v>
       </c>
       <c r="B5" s="3">
-        <v>311.96413405599498</v>
+        <v>311.02791200644378</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -490,7 +490,7 @@
         <v>2028</v>
       </c>
       <c r="B6" s="3">
-        <v>325.75370820804005</v>
+        <v>324.2884009375079</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -498,7 +498,7 @@
         <v>2029</v>
       </c>
       <c r="B7" s="3">
-        <v>340.15281510611749</v>
+        <v>338.11424287999961</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -506,7 +506,7 @@
         <v>2030</v>
       </c>
       <c r="B8" s="3">
-        <v>355.18839758141178</v>
+        <v>352.52954132129344</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -514,7 +514,7 @@
         <v>2031</v>
       </c>
       <c r="B9" s="3">
-        <v>370.88858940383392</v>
+        <v>367.55942738652629</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -522,7 +522,7 @@
         <v>2032</v>
       </c>
       <c r="B10" s="3">
-        <v>387.2827679244121</v>
+        <v>383.23010365131864</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -530,7 +530,7 @@
         <v>2033</v>
       </c>
       <c r="B11" s="3">
-        <v>404.40160904460436</v>
+        <v>399.56888982242469</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -538,7 +538,7 @@
         <v>2034</v>
       </c>
       <c r="B12" s="3">
-        <v>422.27714461538881</v>
+        <v>416.6042703659499</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -546,7 +546,7 @@
         <v>2035</v>
       </c>
       <c r="B13" s="3">
-        <v>440.9428223735332</v>
+        <v>434.36594416616907</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -554,7 +554,7 @@
         <v>2036</v>
       </c>
       <c r="B14" s="3">
-        <v>460.43356852719359</v>
+        <v>452.88487630151832</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -562,7 +562,7 @@
         <v>2037</v>
       </c>
       <c r="B15" s="3">
-        <v>480.78585310794875</v>
+        <v>472.19335202802552</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -570,7 +570,7 @@
         <v>2038</v>
       </c>
       <c r="B16" s="3">
-        <v>502.03775821155375</v>
+        <v>492.32503306429209</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -578,7 +578,7 @@
         <v>2039</v>
       </c>
       <c r="B17" s="3">
-        <v>524.22904925510079</v>
+        <v>513.31501627615114</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -586,7 +586,7 @@
         <v>2040</v>
       </c>
       <c r="B18" s="3">
-        <v>547.40124938392</v>
+        <v>535.1998948633111</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -594,7 +594,7 @@
         <v>2041</v>
       </c>
       <c r="B19" s="3">
-        <v>571.59771716744672</v>
+        <v>558.01782215465528</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -602,7 +602,7 @@
         <v>2042</v>
       </c>
       <c r="B20" s="3">
-        <v>596.86372772943469</v>
+        <v>581.80857812341549</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -610,7 +610,7 @@
         <v>2043</v>
       </c>
       <c r="B21" s="3">
-        <v>623.24655746432268</v>
+        <v>606.61363873818073</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -618,7 +618,7 @@
         <v>2044</v>
       </c>
       <c r="B22" s="3">
-        <v>650.79557249827042</v>
+        <v>632.47624827064465</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -626,7 +626,7 @@
         <v>2045</v>
       </c>
       <c r="B23" s="3">
-        <v>679.56232106038794</v>
+        <v>659.44149468615001</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -634,7 +634,7 @@
         <v>2046</v>
       </c>
       <c r="B24" s="3">
-        <v>709.60062993699773</v>
+        <v>687.55638824846449</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -642,7 +642,7 @@
         <v>2047</v>
       </c>
       <c r="B25" s="3">
-        <v>740.9667051894105</v>
+        <v>716.86994347582402</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -650,7 +650,7 @@
         <v>2048</v>
       </c>
       <c r="B26" s="3">
-        <v>773.71923732367156</v>
+        <v>747.43326459112245</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -658,7 +658,7 @@
         <v>2049</v>
       </c>
       <c r="B27" s="3">
-        <v>807.91951110906598</v>
+        <v>779.2996346152197</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -666,7 +666,7 @@
         <v>2050</v>
       </c>
       <c r="B28" s="3">
-        <v>843.63152025086936</v>
+        <v>812.52460825868923</v>
       </c>
     </row>
   </sheetData>
